--- a/BABA.xlsx
+++ b/BABA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FFBEAD-26A9-4D1D-BEA6-0D0E05B7EBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F0CCAD-E53F-4D18-A96A-DC615704299F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{A3926FB3-B729-449F-AF60-A6E01109C263}"/>
   </bookViews>
@@ -888,7 +888,7 @@
         <v>8</v>
       </c>
       <c r="J2" s="2">
-        <v>177</v>
+        <v>124.3</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -897,7 +897,7 @@
       </c>
       <c r="J3" s="3">
         <f>+J2*J10</f>
-        <v>166.38</v>
+        <v>116.84199999999998</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>16</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="J5" s="3">
         <f>+J3*J4</f>
-        <v>3089676.6</v>
+        <v>2169755.94</v>
       </c>
       <c r="K5" s="28" t="s">
         <v>16</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="J8" s="3">
         <f>+J5-J6+J7</f>
-        <v>2790322.6</v>
+        <v>1870401.94</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="J11" s="16">
         <f>+J5/Model!Q26</f>
-        <v>23.864034911562523</v>
+        <v>16.758754460492778</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J12" s="16">
         <f>+J8/Model!Q19</f>
-        <v>19.802864341222811</v>
+        <v>13.274205599517405</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">

--- a/BABA.xlsx
+++ b/BABA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F0CCAD-E53F-4D18-A96A-DC615704299F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFB58A5-6954-4965-AF34-AD2DC3D46BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{A3926FB3-B729-449F-AF60-A6E01109C263}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A3926FB3-B729-449F-AF60-A6E01109C263}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -888,7 +888,7 @@
         <v>8</v>
       </c>
       <c r="J2" s="2">
-        <v>124.3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -897,7 +897,7 @@
       </c>
       <c r="J3" s="3">
         <f>+J2*J10</f>
-        <v>116.84199999999998</v>
+        <v>104.33999999999999</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>16</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="J5" s="3">
         <f>+J3*J4</f>
-        <v>2169755.94</v>
+        <v>1937593.7999999998</v>
       </c>
       <c r="K5" s="28" t="s">
         <v>16</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="J8" s="3">
         <f>+J5-J6+J7</f>
-        <v>1870401.94</v>
+        <v>1638239.7999999998</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="J11" s="16">
         <f>+J5/Model!Q26</f>
-        <v>16.758754460492778</v>
+        <v>14.965581215725649</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J12" s="16">
         <f>+J8/Model!Q19</f>
-        <v>13.274205599517405</v>
+        <v>11.626555480642985</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
